--- a/business_forms/015_digitalization_advisory_network_application_form--business_forms.xlsx
+++ b/business_forms/015_digitalization_advisory_network_application_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'al'}</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'AL'}</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'ak'}</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'AK'}</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'ar'}</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'AR'}</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'az'}</t>
+          <t>az</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'AZ'}</t>
+          <t>AZ</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'ca'}</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'CA'}</t>
+          <t>CA</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'co'}</t>
+          <t>co</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'CO'}</t>
+          <t>CO</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'ct'}</t>
+          <t>ct</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'CT'}</t>
+          <t>CT</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'fl'}</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'FL'}</t>
+          <t>FL</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'ga'}</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'GA'}</t>
+          <t>GA</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'hi'}</t>
+          <t>hi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'HI'}</t>
+          <t>HI</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'ia'}</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'IA'}</t>
+          <t>IA</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'id'}</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'ID'}</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'il'}</t>
+          <t>il</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'IL'}</t>
+          <t>IL</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'in'}</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'IN'}</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'ks'}</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'KS'}</t>
+          <t>KS</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'ky'}</t>
+          <t>ky</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'KY'}</t>
+          <t>KY</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'la'}</t>
+          <t>la</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'LA'}</t>
+          <t>LA</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'ma'}</t>
+          <t>ma</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'MA'}</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'md'}</t>
+          <t>md</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'MD'}</t>
+          <t>MD</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'me'}</t>
+          <t>me</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'ME'}</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'mi'}</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'MI'}</t>
+          <t>MI</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'mn'}</t>
+          <t>mn</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'MN'}</t>
+          <t>MN</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'mo'}</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'MO'}</t>
+          <t>MO</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'MS'}</t>
+          <t>MS</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'mt'}</t>
+          <t>mt</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'MT'}</t>
+          <t>MT</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'nc'}</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'NC'}</t>
+          <t>NC</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'nd'}</t>
+          <t>nd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'ND'}</t>
+          <t>ND</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'ne'}</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'NE'}</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'nh'}</t>
+          <t>nh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'NH'}</t>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'nj'}</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'NJ'}</t>
+          <t>NJ</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'nm'}</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'NM'}</t>
+          <t>NM</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'nv'}</t>
+          <t>nv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'NV'}</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'ny'}</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'NY'}</t>
+          <t>NY</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'oh'}</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'OH'}</t>
+          <t>OH</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'ok'}</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'OK'}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'or'}</t>
+          <t>or</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'OR'}</t>
+          <t>OR</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'pa'}</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'PA'}</t>
+          <t>PA</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'ri'}</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'RI'}</t>
+          <t>RI</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'sc'}</t>
+          <t>sc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'SC'}</t>
+          <t>SC</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'sd'}</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'SD'}</t>
+          <t>SD</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'tn'}</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'TN'}</t>
+          <t>TN</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'tx'}</t>
+          <t>tx</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'TX'}</t>
+          <t>TX</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'ut'}</t>
+          <t>ut</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'UT'}</t>
+          <t>UT</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'va'}</t>
+          <t>va</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'VA'}</t>
+          <t>VA</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'vt'}</t>
+          <t>vt</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'VT'}</t>
+          <t>VT</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'wa'}</t>
+          <t>wa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'WA'}</t>
+          <t>WA</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'wv'}</t>
+          <t>wv</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'WV'}</t>
+          <t>WV</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'wi'}</t>
+          <t>wi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'WI'}</t>
+          <t>WI</t>
         </is>
       </c>
     </row>
@@ -1648,29 +1648,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'wv'}</t>
+          <t>wy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'WV'}</t>
+          <t>WY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>state_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'wy'}</t>
+          <t>business_forms</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'WY'}</t>
+          <t>Business Forms</t>
         </is>
       </c>
     </row>
@@ -1682,29 +1682,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'business_forms'}</t>
+          <t>registration_forms</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Business Forms'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'value':_'registration_forms'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'value': 'Registration Forms'}</t>
+          <t>Registration Forms</t>
         </is>
       </c>
     </row>
